--- a/docs/review/packs/chapter-3.4.xlsx
+++ b/docs/review/packs/chapter-3.4.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -1852,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Expect inverse dynamics to underestimate joint load where co-contraction is likely, which includes most symptomatic knees.</t>
+          <t>Read a joint moment as a net quantity rather than as a muscle force.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Treat instrumented implant data as the direct measurement and the rest as computed.</t>
+          <t>Expect inverse dynamics to underestimate joint load where co-contraction is likely, which includes most symptomatic knees.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Treat the kinetic account as the one that explains disease progression, since cartilage responds to load rather than to motion.</t>
+          <t>Treat instrumented implant data as the direct measurement and the rest as computed.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Address muscle capacity alongside any mechanical correction, since co-contraction and weakness both raise load.</t>
+          <t>State the activity and the method with any kinetic figure, since both change it by more than most clinical variables do.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -2041,22 +2041,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>3.4.2-P1</t>
+          <t>3.4.1-P5</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Treat the ground reaction force as a vector with a point of application, not as a number.</t>
+          <t>Treat the kinetic account as the one that explains disease progression, since cartilage responds to load rather than to motion.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -2066,22 +2066,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3.4.2-P2</t>
+          <t>3.4.1-P6</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Use a walking aid to reduce limb load when the aim is mechanical rather than only balance.</t>
+          <t>Correct alignment where compartment load is the problem, because it is the largest modifiable term.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -2091,22 +2091,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3.4.2-P3</t>
+          <t>3.4.1-P7</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Consider foot progression angle and stance width, since they change the knee moment without changing the force.</t>
+          <t>Address muscle capacity alongside any mechanical correction, since co-contraction and weakness both raise load.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2116,12 +2116,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.4.2-P4</t>
+          <t>3.4.1-P8</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Treat the ground reaction force as the input that alignment surgery works on.</t>
+          <t>Read a modelled muscle force with the model's assumptions in mind rather than as a measurement.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2141,7 +2141,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.4.2-P5</t>
+          <t>3.4.2-P1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Plan an osteotomy by where the force line should fall rather than by a target angle alone.</t>
+          <t>Treat the ground reaction force as a vector with a point of application, not as a number.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.4.2-P6</t>
+          <t>3.4.2-P2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Expect a lateral wedge or a gait modification to produce a small mechanical change, and describe it as such.</t>
+          <t>Use a walking aid to reduce limb load when the aim is mechanical rather than only balance.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2191,7 +2191,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.4.2-P7</t>
+          <t>3.4.2-P3</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Treat static alignment as a proxy for the dynamic moment, since they correlate imperfectly.</t>
+          <t>Consider foot progression angle and stance width, since they change the knee moment without changing the force.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2216,12 +2216,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.4.3-P1</t>
+          <t>3.4.2-P4</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Expect the medial compartment to carry more load in a normally aligned knee, and much more in a varus one.</t>
+          <t>Read an insole or accelerometer figure as a proxy rather than as a ground reaction force.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2241,22 +2241,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.4.3-P2</t>
+          <t>3.4.2-P5</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Preserve meniscal tissue to preserve contact area, since the force will not fall.</t>
+          <t>Treat the ground reaction force as the input that alignment surgery works on.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2266,12 +2266,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.4.3-P3</t>
+          <t>3.4.2-P6</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Treat compartment load division as the quantity unicompartmental and osteotomy surgery manipulate, and treat the published division as a population statement rather than a patient's.</t>
+          <t>Plan an osteotomy by where the force line should fall rather than by a target angle alone.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2291,12 +2291,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.4.3-P4</t>
+          <t>3.4.2-P7</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Plan osteotomy correction to a target that avoids lateral overload rather than to the largest achievable correction.</t>
+          <t>Expect a lateral wedge or a gait modification to produce a small mechanical change, and describe it as such.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2316,12 +2316,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.4.3-P5</t>
+          <t>3.4.2-P8</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Treat intraoperative balance measurement as informative about an anaesthetised knee.</t>
+          <t>Treat static alignment as a proxy for the dynamic moment, since they correlate imperfectly.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.4.3-P6</t>
+          <t>3.4.3-P1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Expect activity and mass to multiply the loading cycles a construct must survive.</t>
+          <t>Expect the medial compartment to carry more load in a normally aligned knee, and much more in a varus one.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2366,12 +2366,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.4.4-P1</t>
+          <t>3.4.3-P2</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>3.4.4</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Expect extension weakness after patellectomy to be mechanical and permanent rather than a rehabilitation failure.</t>
+          <t>Preserve meniscal tissue to preserve contact area, since the force will not fall.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2391,22 +2391,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.4.4-P2</t>
+          <t>3.4.3-P3</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.4.4</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Treat tubercle transfer as a load changing operation and plan it as such.</t>
+          <t>Treat compartment load division as the quantity unicompartmental and osteotomy surgery manipulate, and treat the published division as a population statement rather than a patient's.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2416,12 +2416,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.4.4-P3</t>
+          <t>3.4.3-P4</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3.4.4</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Treat the extensor lever arm as a surgical variable in every operation that touches the extensor mechanism, the joint line or the tubercle.</t>
+          <t>Plan osteotomy correction to a target that avoids lateral overload rather than to the largest achievable correction.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.4.4-P4</t>
+          <t>3.4.3-P5</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.4.4</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Restore the joint line in arthroplasty, since raising it shortens the extensor arm and raises patellofemoral load.</t>
+          <t>Read the compartment load division as an average over a cycle, not a constant.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2466,12 +2466,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.4.4-P5</t>
+          <t>3.4.3-P6</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.4.4</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Measure patellar height before and after any procedure that alters the extensor mechanism.</t>
+          <t>Treat intraoperative balance measurement as informative about an anaesthetised knee.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2491,12 +2491,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.4.4-P6</t>
+          <t>3.4.3-P7</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.4.4</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Plan tubercle transfer by the load change intended rather than by tracking alone.</t>
+          <t>Expect activity and mass to multiply the loading cycles a construct must survive.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.4.4-P7</t>
+          <t>3.4.4-P1</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>- Patellar height should be measured before and after extensor mechanism surgery.</t>
+          <t>Expect extension weakness after patellectomy to be mechanical and permanent rather than a rehabilitation failure.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2541,12 +2541,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.4.5-P1</t>
+          <t>3.4.4-P2</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.4.5</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Keep the external and the internal moment distinct.</t>
+          <t>Treat tubercle transfer as a load changing operation and plan it as such.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2566,12 +2566,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.4.5-P2</t>
+          <t>3.4.4-P3</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.4.5</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Treat a net internal moment as unable to separate co-contraction from a single strong agonist.</t>
+          <t>Read the shape of a moment arm curve rather than a single published value.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2591,22 +2591,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.4.5-P3</t>
+          <t>3.4.4-P4</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.4.5</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Expect normalised figures to hide absolute load, which matters in a heavy patient.</t>
+          <t>Treat the extensor lever arm as a surgical variable in every operation that touches the extensor mechanism, the joint line or the tubercle.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2616,22 +2616,22 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.4.5-P4</t>
+          <t>3.4.4-P5</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.4.5</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Use the moment against angle curve rather than a peak value when comparing activities.</t>
+          <t>Restore the joint line in arthroplasty, since raising it shortens the extensor arm and raises patellofemoral load.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2641,12 +2641,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.4.5-P5</t>
+          <t>3.4.4-P6</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.4.5</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Treat the knee adduction moment as the kinetic variable with the clearest clinical application, since it is associated with progression and is modifiable by three different routes: osteotomy, gait modification and bracing.</t>
+          <t>Measure patellar height before and after any procedure that alters the extensor mechanism.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2666,12 +2666,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.4.5-P6</t>
+          <t>3.4.4-P7</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.4.5</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>No agreed moment threshold defines who should be offered an osteotomy, so the decision remains clinical.</t>
+          <t>Plan tubercle transfer by the load change intended rather than by tracking alone.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2691,12 +2691,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.4.5-P7</t>
+          <t>3.4.4-P8</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.4.5</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Plan osteotomy to a target that changes the moment rather than to an angle alone.</t>
+          <t>- Patellar height should be measured before and after extensor mechanism surgery.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.4.5-P8</t>
+          <t>3.4.5-P1</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Address body mass alongside any mechanical correction, since it scales every moment.</t>
+          <t>Keep the external and the internal moment distinct.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2741,12 +2741,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.4.6-P1</t>
+          <t>3.4.5-P2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.4.6</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Measure alignment when the adduction moment is the clinical question, since it is the available proxy.</t>
+          <t>Read a quoted moment as external unless the paper says otherwise, since that is the convention.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.4.6-P2</t>
+          <t>3.4.5-P3</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.4.6</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Prefer impulse over peak when the question is cumulative exposure rather than a single step.</t>
+          <t>Treat a net internal moment as unable to separate co-contraction from a single strong agonist.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2791,22 +2791,22 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.4.6-P3</t>
+          <t>3.4.5-P4</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.4.6</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Treat the adduction moment as the target of every mechanical treatment for medial compartment disease, and treat alignment as the lever that moves it furthest.</t>
+          <t>Expect normalised figures to hide absolute load, which matters in a heavy patient.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2816,22 +2816,22 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.4.6-P4</t>
+          <t>3.4.5-P5</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.4.6</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Address body mass alongside correction, since it can exceed the surgical effect.</t>
+          <t>Use the moment against angle curve rather than a peak value when comparing activities.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2841,12 +2841,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.4.6-P5</t>
+          <t>3.4.5-P6</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.4.6</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Plan correction to a mechanical axis target and confirm it radiographically.</t>
+          <t>Treat the knee adduction moment as the kinetic variable with the clearest clinical application, since it is associated with progression and is modifiable by three different routes: osteotomy, gait modification and bracing.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2866,22 +2866,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.4.7-P1</t>
+          <t>3.4.5-P7</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.4.7</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Measure strength through range rather than at one angle, since both the arm and the muscle change.</t>
+          <t>No agreed moment threshold defines who should be offered an osteotomy, so the decision remains clinical.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2891,22 +2891,22 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.4.7-P2</t>
+          <t>3.4.5-P8</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.4.7</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Treat effusion as a cause of reduced internal moment before concluding muscle failure.</t>
+          <t>Compare unlike treatments by the moment change each produces.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2916,22 +2916,22 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.4.7-P3</t>
+          <t>3.4.5-P9</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.4.7</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Expect co-contraction to raise joint load in painful and unstable knees, and read modelled loads accordingly.</t>
+          <t>Plan osteotomy to a target that changes the moment rather than to an angle alone.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2941,12 +2941,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.4.7-P4</t>
+          <t>3.4.5-P10</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.4.7</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Treat the internal moment as the half of the equation surgery usually cannot fix.</t>
+          <t>Address body mass alongside any mechanical correction, since it scales every moment.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2966,12 +2966,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.4.7-P5</t>
+          <t>3.4.5-P11</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.4.7</t>
+          <t>3.4.5</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Expect a hamstring graft to remove part of the internal flexion moment, and account for it in rehabilitation.</t>
+          <t>State that no moment threshold defines the indication, and decide clinically.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2991,22 +2991,22 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.4.7-P6</t>
+          <t>3.4.6-P1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.4.7</t>
+          <t>3.4.6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Treat a quadriceps deficit as a mechanical problem rather than a motivational one.</t>
+          <t>Measure alignment when the adduction moment is the clinical question, since it is the available proxy.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3016,12 +3016,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.4.8-P1</t>
+          <t>3.4.6-P2</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.4.8</t>
+          <t>3.4.6</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Use loading rate as the practical measure of whether a landing is being absorbed.</t>
+          <t>Offer a cane in the opposite hand for medial compartment pain, on mechanical grounds.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3041,12 +3041,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.4.8-P2</t>
+          <t>3.4.6-P3</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.4.8</t>
+          <t>3.4.6</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Expect absorption and joint force to rise together, so a well absorbed landing is not an unloaded one.</t>
+          <t>Prefer impulse over peak when the question is cumulative exposure rather than a single step.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3066,12 +3066,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.4.8-P3</t>
+          <t>3.4.6-P4</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.4.8</t>
+          <t>3.4.6</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Treat eccentric capacity as a return to activity criterion rather than a rehabilitation stage.</t>
+          <t>Treat the adduction moment as the target of every mechanical treatment for medial compartment disease, and treat alignment as the lever that moves it furthest.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3091,12 +3091,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.4.8-P4</t>
+          <t>3.4.6-P5</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.4.8</t>
+          <t>3.4.6</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Expect asymmetry to persist behind a normal examination after reconstruction.</t>
+          <t>Address body mass alongside correction, since it can exceed the surgical effect.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3116,12 +3116,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.4.8-P5</t>
+          <t>3.4.6-P6</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.4.8</t>
+          <t>3.4.6</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Prefer graded exposure to avoidance, since cumulative cycles rather than peaks drive the cartilage consequence.</t>
+          <t>State the observational nature of the progression association when counselling.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3141,22 +3141,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.4.9-P1</t>
+          <t>3.4.6-P7</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.4.9</t>
+          <t>3.4.6</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Preserve meniscal tissue and repair roots where feasible, on load path grounds.</t>
+          <t>Plan correction to a mechanical axis target and confirm it radiographically.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3166,12 +3166,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.4.9-P2</t>
+          <t>3.4.7-P1</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.4.9</t>
+          <t>3.4.7</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Expect subchondral change to mark where load concentrated, and look for the cause.</t>
+          <t>Measure strength through range rather than at one angle, since both the arm and the muscle change.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3191,12 +3191,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.4.9-P3</t>
+          <t>3.4.7-P2</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.4.9</t>
+          <t>3.4.7</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Address alignment before or with any procedure intended to protect a compartment.</t>
+          <t>Treat effusion as a cause of reduced internal moment before concluding muscle failure.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3216,22 +3216,22 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.4.9-P4</t>
+          <t>3.4.7-P3</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.4.9</t>
+          <t>3.4.7</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Treat every reconstructive decision as a load path decision.</t>
+          <t>Expect co-contraction to raise joint load in painful and unstable knees, and read modelled loads accordingly.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3241,12 +3241,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.4.9-P5</t>
+          <t>3.4.7-P4</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.4.9</t>
+          <t>3.4.7</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Plan reconstruction as a combination when the path has more than one failed part.</t>
+          <t>Treat the internal moment as the half of the equation surgery usually cannot fix.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3266,12 +3266,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.4.9-P6</t>
+          <t>3.4.7-P5</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>3.4.9</t>
+          <t>3.4.7</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Consider subchondral bone when a surface procedure has failed without a technical cause.</t>
+          <t>Expect a hamstring graft to remove part of the internal flexion moment, and account for it in rehabilitation.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3291,22 +3291,22 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.4.10-P1</t>
+          <t>3.4.7-P6</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>3.4.10</t>
+          <t>3.4.7</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Expect a meniscectomised knee to absorb fast loads less well, and advise on activity accordingly.</t>
+          <t>Treat a quadriceps deficit as a mechanical problem rather than a motivational one.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3316,12 +3316,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.4.10-P2</t>
+          <t>3.4.8-P1</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>3.4.10</t>
+          <t>3.4.8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Treat accelerometry as a proxy for loading rate rather than a measurement of it.</t>
+          <t>Read a reduced knee contribution in a power curve as a strategy change rather than necessarily as weakness.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3341,31 +3341,456 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.4.10-P3</t>
+          <t>3.4.8-P2</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>3.4.10</t>
+          <t>3.4.8</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Treat shock absorption as the mechanical account of activity advice.</t>
+          <t>Use loading rate as the practical measure of whether a landing is being absorbed.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8-P3</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Expect absorption and joint force to rise together, so a well absorbed landing is not an unloaded one.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8-P4</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Treat eccentric capacity as a return to activity criterion rather than a rehabilitation stage.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8-P5</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Expect asymmetry to persist behind a normal examination after reconstruction.</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8-P6</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Prefer graded exposure to avoidance, since cumulative cycles rather than peaks drive the cartilage consequence.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8-P7</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>3.4.8</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>State the uncertainty about individual tolerance rather than offering a figure.</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9-P1</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Preserve meniscal tissue and repair roots where feasible, on load path grounds.</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9-P2</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Read extrusion as a functional loss rather than an incidental measurement.</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9-P3</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Expect subchondral change to mark where load concentrated, and look for the cause.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9-P4</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Address alignment before or with any procedure intended to protect a compartment.</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9-P5</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Treat every reconstructive decision as a load path decision.</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9-P6</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Correct alignment before or with a cartilage or meniscal procedure.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9-P7</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Plan reconstruction as a combination when the path has more than one failed part.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9-P8</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>3.4.9</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Consider subchondral bone when a surface procedure has failed without a technical cause.</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>3.4.10-P1</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>3.4.10</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Expect a meniscectomised knee to absorb fast loads less well, and advise on activity accordingly.</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>3.4.10-P2</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>3.4.10</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Read subchondral sclerosis as evidence of concentrated load and look for its cause.</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>3.4.10-P3</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>3.4.10</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Treat accelerometry as a proxy for loading rate rather than a measurement of it.</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>3.4.10-P4</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>3.4.10</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Treat shock absorption as the mechanical account of activity advice.</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3666,7 +4091,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>57</f>
+        <f>74</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -3681,7 +4106,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E59,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E76,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -3711,7 +4136,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E59,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E76,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -3723,7 +4148,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E59,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E76,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -3735,7 +4160,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E59,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E76,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -3747,7 +4172,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E59,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E76,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
